--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -645,7 +650,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -702,7 +708,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -755,7 +762,8 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -808,7 +816,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -861,7 +870,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -922,7 +932,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -979,7 +990,8 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1032,7 +1044,8 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1093,7 +1106,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -1150,7 +1164,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1207,7 +1222,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1260,7 +1276,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1310,10 +1327,11 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1366,7 +1384,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1419,7 +1438,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1472,7 +1492,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1533,7 +1554,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1590,7 +1612,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1643,7 +1666,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1696,7 +1720,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1749,7 +1774,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1802,7 +1828,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1859,7 +1886,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1912,7 +1940,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1973,7 +2002,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2038,7 +2068,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2095,7 +2126,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -2156,7 +2188,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2213,7 +2246,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -2274,7 +2308,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -2331,7 +2366,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2392,7 +2428,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -2457,7 +2494,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -2514,7 +2552,8 @@
           <t>6.4</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2562,8 +2601,13 @@
       </c>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -2624,7 +2668,8 @@
           <t>6.6</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2681,7 +2726,8 @@
           <t>6.4</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -2729,8 +2775,13 @@
       </c>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2783,7 +2834,8 @@
           <t>6.6</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -2836,7 +2888,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2884,8 +2937,13 @@
       </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -2933,8 +2991,13 @@
       </c>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2982,8 +3045,13 @@
       </c>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -3031,8 +3099,13 @@
       </c>
       <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3080,8 +3153,13 @@
       </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -3129,8 +3207,13 @@
       </c>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3190,8 +3273,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3243,8 +3331,13 @@
       </c>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -3300,8 +3393,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3358,7 +3456,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3423,7 +3522,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3480,7 +3580,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -3533,7 +3634,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -3586,7 +3688,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -3634,8 +3737,13 @@
       </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -3696,7 +3804,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3761,7 +3870,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3813,8 +3923,13 @@
       </c>
       <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3866,8 +3981,13 @@
       </c>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -3923,8 +4043,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr">
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3984,8 +4109,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4037,8 +4167,13 @@
       </c>
       <c r="L63" s="3" t="inlineStr"/>
       <c r="M63" s="3" t="inlineStr"/>
-      <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr">
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
